--- a/pre-week-2/homework2.xlsx
+++ b/pre-week-2/homework2.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr hidePivotFieldList="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A25E1D6-84D4-4C2E-9E7A-337B167203B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F42E6AD9-977F-4A65-816C-D3FDA2E05043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="14807" r:id="rId4"/>
+    <pivotCache cacheId="1555" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t xml:space="preserve">Categorical </t>
   </si>
@@ -92,6 +92,9 @@
     <t>Store L</t>
   </si>
   <si>
+    <t>avg</t>
+  </si>
+  <si>
     <t>Grand Total</t>
   </si>
   <si>
@@ -101,10 +104,19 @@
     <t>South</t>
   </si>
   <si>
+    <t>median</t>
+  </si>
+  <si>
     <t>Store J</t>
   </si>
   <si>
+    <t>mode</t>
+  </si>
+  <si>
     <t>Store F</t>
+  </si>
+  <si>
+    <t>Range</t>
   </si>
   <si>
     <t>Store D</t>
@@ -437,7 +449,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5480-4D73-B692-29EC597008B4}"/>
+                <c16:uniqueId val="{00000001-6BA4-41E9-84CB-A508A9196778}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -457,7 +469,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5480-4D73-B692-29EC597008B4}"/>
+                <c16:uniqueId val="{00000003-6BA4-41E9-84CB-A508A9196778}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -477,7 +489,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5480-4D73-B692-29EC597008B4}"/>
+                <c16:uniqueId val="{00000005-6BA4-41E9-84CB-A508A9196778}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -497,7 +509,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5480-4D73-B692-29EC597008B4}"/>
+                <c16:uniqueId val="{00000007-6BA4-41E9-84CB-A508A9196778}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2412,7 +2424,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A7D124E-629B-4B3C-BCA7-C89D907D1C54}" name="PivotTable2" cacheId="14807" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A7D124E-629B-4B3C-BCA7-C89D907D1C54}" name="PivotTable2" cacheId="1555" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="M2:N6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -2475,7 +2487,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CB39E4F-71E6-4DD8-9505-AF05EEC1BCBC}" name="PivotTable1" cacheId="14807" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1CB39E4F-71E6-4DD8-9505-AF05EEC1BCBC}" name="PivotTable1" cacheId="1555" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="C16:D21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3041,8 +3053,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="4">
+        <f>AVERAGE(F3:F14)</f>
+        <v>49.416666666666664</v>
+      </c>
       <c r="M6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="4">
         <v>593</v>
@@ -3050,10 +3069,10 @@
     </row>
     <row r="7" spans="3:14">
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -3065,13 +3084,20 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="4">
+        <f>MEDIAN(F3:F14)</f>
+        <v>47.5</v>
+      </c>
     </row>
     <row r="8" spans="3:14">
       <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -3083,10 +3109,17 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.MODE.SNGL(F3:F14)</f>
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="3:14">
       <c r="C9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -3101,13 +3134,20 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="4">
+        <f>MAX(F3:F14)-MIN(F3:F14)</f>
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="3:14">
       <c r="C10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -3122,7 +3162,7 @@
     </row>
     <row r="11" spans="3:14">
       <c r="C11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -3140,7 +3180,7 @@
     </row>
     <row r="12" spans="3:14">
       <c r="C12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -3158,7 +3198,7 @@
     </row>
     <row r="13" spans="3:14">
       <c r="C13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -3176,7 +3216,7 @@
     </row>
     <row r="14" spans="3:14">
       <c r="C14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -3221,7 +3261,7 @@
     </row>
     <row r="19" spans="3:4">
       <c r="C19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>143</v>
@@ -3237,7 +3277,7 @@
     </row>
     <row r="21" spans="3:4">
       <c r="C21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <v>593</v>
@@ -3259,17 +3299,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3284,22 +3324,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
